--- a/faculty_data.xlsx
+++ b/faculty_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nivis\my_projects\projects_myTimetable\college_Timetable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drlak\my_projects\projects_myTimetable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A659D23-BD3B-490D-A8F2-0E2774DF39B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1641C0AF-0C29-42C7-AEF7-822868A20531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{133CB0F7-179D-4473-A91B-779EACBBF9B7}"/>
+    <workbookView xWindow="990" yWindow="5100" windowWidth="17925" windowHeight="10305" xr2:uid="{133CB0F7-179D-4473-A91B-779EACBBF9B7}"/>
   </bookViews>
   <sheets>
     <sheet name="CE" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="38">
   <si>
     <t>Rosa</t>
   </si>
@@ -123,6 +123,33 @@
   </si>
   <si>
     <t>position</t>
+  </si>
+  <si>
+    <t>ROSA</t>
+  </si>
+  <si>
+    <t>ZVL</t>
+  </si>
+  <si>
+    <t>ELVIZ</t>
+  </si>
+  <si>
+    <t>NIVI</t>
+  </si>
+  <si>
+    <t>CHINO</t>
+  </si>
+  <si>
+    <t>ANJANA</t>
+  </si>
+  <si>
+    <t>EZRI</t>
+  </si>
+  <si>
+    <t>EZER</t>
+  </si>
+  <si>
+    <t>ZADIE</t>
   </si>
 </sst>
 </file>
@@ -519,7 +546,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
@@ -536,7 +563,7 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -553,7 +580,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -570,7 +597,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -587,7 +614,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
@@ -604,7 +631,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
@@ -621,7 +648,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -638,7 +665,7 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
@@ -655,7 +682,7 @@
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -896,7 +923,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
@@ -913,7 +940,7 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -930,7 +957,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -947,7 +974,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -964,7 +991,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
@@ -981,7 +1008,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
@@ -998,7 +1025,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -1015,7 +1042,7 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
@@ -1032,7 +1059,7 @@
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
